--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18035,7 +18053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18079,6 +18097,64 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1997_98_0254 'Art.Pardubice' prev→CLUB_S1996_97_0266 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1997_98_0453 'M.Hoštice' prev→CLUB_S1996_97_0446 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0021</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1997_98_0021 'Baráž o Extraligu' (L15, parent=NODE_S1997_98_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0027</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1997_98_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1997_98_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -21066,8 +21142,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -21147,7 +21221,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -44361,6 +44434,149 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0254</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0254 'Art.Pardubice' prev→CLUB_S1996_97_0266 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0453</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0453 'M.Hoštice' prev→CLUB_S1996_97_0446 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0021</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1997_98_0021 'Baráž o Extraligu' (L15, parent=NODE_S1997_98_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0027</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1997_98_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1997_98_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18053,7 +18053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18103,7 +18103,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1997_98_0254 'Art.Pardubice' prev→CLUB_S1996_97_0266 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18115,7 +18115,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1997_98_0453 'M.Hoštice' prev→CLUB_S1996_97_0446 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18125,14 +18125,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1997_98_0021</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1997_98_0021 'Baráž o Extraligu' (L15, parent=NODE_S1997_98_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18142,17 +18137,492 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1997_98_0027</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1997_98_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1997_98_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0467 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tachov + Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0266 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0275 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0423 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0446 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Škoda Team Šumperk' → 'Šumperk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0261 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0471 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0213 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21142,6 +21612,8 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -21172,6 +21644,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0001</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21184,6 +21661,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0003</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21196,6 +21678,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0003</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21208,6 +21695,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0032</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21221,6 +21713,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -23281,12 +23774,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -23575,12 +24068,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -23973,12 +24466,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24272,12 +24765,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -24818,12 +25311,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -25253,12 +25746,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -25725,12 +26218,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -25767,12 +26260,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -25982,12 +26475,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -29607,12 +30100,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29859,12 +30352,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -30326,12 +30819,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -30373,12 +30866,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -30702,12 +31195,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -30749,12 +31242,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -30838,12 +31331,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -32124,12 +32617,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Tábor = Klub rozhodčích LH Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. Klub rozhodci ledniho hokeje. city Tábor.</t>
+          <t>Tábor = Klub rozhodčích LH Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. Klub rozhodci ledniho hokeje. city Tábor. || TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Klub rozhodčích LH Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -33718,12 +34211,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Tachov+Cheb = HC Tachov + Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. Spojeny klub Tachov-Cheb. city Tachov+Cheb.</t>
+          <t>Tachov+Cheb = HC Tachov + Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. Spojeny klub Tachov-Cheb. city Tachov+Cheb. || TBD: city 'Tachov + Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Tachov + Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -33760,12 +34253,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -34180,12 +34673,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -34746,12 +35239,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -40628,12 +41121,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -40675,12 +41168,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -41691,12 +42184,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec.</t>
+          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec. || TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Český Těšín</t>
         </is>
       </c>
     </row>
@@ -42702,12 +43195,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -43095,12 +43588,12 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava.</t>
+          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava. || TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>NH Válcovny Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
@@ -44002,12 +44495,12 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>Šumperk = HC Škoda Team Šumperk (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Post-revolucni sponzor Škoda. city Šumperk.</t>
+          <t>Šumperk = HC Škoda Team Šumperk (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Post-revolucni sponzor Škoda. city Šumperk. || TBD: city 'Škoda Team Šumperk' → 'Šumperk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>Škoda Team Šumperk</t>
+          <t>Šumperk</t>
         </is>
       </c>
     </row>
@@ -44444,11 +44937,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -44493,21 +44986,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0254</t>
+          <t>CLUB_S1997_98_0003</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0254 'Art.Pardubice' prev→CLUB_S1996_97_0266 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -44515,21 +45006,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0453</t>
+          <t>CLUB_S1997_98_0010</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0453 'M.Hoštice' prev→CLUB_S1996_97_0446 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -44537,21 +45026,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1997_98_0021</t>
+          <t>CLUB_S1997_98_0019</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1997_98_0021 'Baráž o Extraligu' (L15, parent=NODE_S1997_98_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -44559,24 +45046,822 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1997_98_0027</t>
+          <t>CLUB_S1997_98_0026</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1997_98_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1997_98_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0041</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0051</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0053</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0467 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0055</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0062</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0063</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0068</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0149</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0155</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0155</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0166</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0167</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0174</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0175</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0177</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0188</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0205</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0234</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0242</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0243</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tachov + Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0245</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0254</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0266 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0256</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0258</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0269</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0270</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0275 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0278</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0296</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0308</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0402</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0403</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0413</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0423 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0427</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0450</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0453</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0446 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0459</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0480</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Škoda Team Šumperk' → 'Šumperk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0483</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0261 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0484</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0471 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1997_98_0485</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0213 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18053,7 +18053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18115,7 +18115,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18127,7 +18127,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18139,7 +18139,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18151,7 +18151,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0467 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18163,7 +18163,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18175,7 +18175,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0467 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -18187,7 +18187,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -18199,7 +18199,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18211,7 +18211,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -18223,7 +18223,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -18235,7 +18235,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -18247,7 +18247,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -18259,7 +18259,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18271,7 +18271,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -18283,7 +18283,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -18295,7 +18295,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18307,7 +18307,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -18319,7 +18319,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tachov + Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -18331,7 +18331,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -18343,7 +18343,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0266 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -18355,7 +18355,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -18367,7 +18367,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -18379,7 +18379,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tachov + Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0275 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -18391,7 +18391,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -18403,7 +18403,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0266 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -18415,7 +18415,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -18427,7 +18427,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -18439,7 +18439,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -18451,7 +18451,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0275 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0423 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -18463,7 +18463,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0446 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -18475,7 +18475,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -18487,7 +18487,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Škoda Team Šumperk' → 'Šumperk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -18499,7 +18499,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0261 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -18511,7 +18511,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0471 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -18523,106 +18523,10 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0423 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0213 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0446 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Škoda Team Šumperk' → 'Šumperk' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0261 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0471 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0213 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -18639,7 +18543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18698,6 +18602,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18740,6 +18649,11 @@
           <t>14 týmů: základ + QF/SF/finále/O3 + baráž. Mistr: HC Petra Vsetín (4. titul).</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18787,6 +18701,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18829,6 +18748,11 @@
           <t>1.liga: základní část + předkolo + čtvrtfinále + semifinále + finále + baráž o 1.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18871,6 +18795,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18913,6 +18842,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18955,6 +18889,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18997,6 +18936,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19039,6 +18983,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19081,6 +19030,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19123,6 +19077,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19165,6 +19124,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19207,6 +19171,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19249,6 +19218,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19291,6 +19265,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19333,6 +19312,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19375,6 +19359,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19417,6 +19406,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19459,6 +19453,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19501,6 +19500,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19543,6 +19547,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19585,6 +19594,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19627,6 +19641,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19669,6 +19688,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19711,6 +19735,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19753,6 +19782,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19795,6 +19829,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19842,6 +19881,11 @@
           <t>Samostatná baráž o 1.ligu: Prostějov–Šumperk 4:1, Přerov–Kadaň 2:4.</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19889,6 +19933,11 @@
           <t>Kvalifikace o 2.ligu</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19931,6 +19980,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -20057,6 +20111,11 @@
           <t>II.liga: 2 skupiny + 1.kolo + 2.kolo.</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -20099,6 +20158,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -20141,6 +20205,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -20183,6 +20252,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0035</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20225,6 +20299,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0036</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20267,6 +20346,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0039</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20309,6 +20393,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0040</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20393,6 +20482,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0042</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -20477,6 +20571,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0044</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20519,6 +20618,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0051</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20561,6 +20665,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0052</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20603,6 +20712,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0055</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -20645,6 +20759,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0056</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20687,6 +20806,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0057</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -20729,6 +20853,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0058</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -20771,6 +20900,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0059</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -20813,6 +20947,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0060</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -20897,6 +21036,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0061</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20939,6 +21083,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0062</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -20981,6 +21130,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0063</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -21023,6 +21177,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0064</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -21065,6 +21224,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0065</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -21107,6 +21271,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0066</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -21149,6 +21318,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0067</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -21191,6 +21365,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0068</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21527,6 +21706,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0082</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -21567,6 +21751,11 @@
       <c r="K69" t="inlineStr">
         <is>
           <t>Kontejner L50</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0083</t>
         </is>
       </c>
     </row>
@@ -21632,6 +21821,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -21649,6 +21843,11 @@
           <t>NODE_S1997_98_0001</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21666,6 +21865,11 @@
           <t>NODE_S1997_98_0003</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21683,6 +21887,11 @@
           <t>NODE_S1997_98_0003</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21700,6 +21909,11 @@
           <t>NODE_S1997_98_0032</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21710,6 +21924,11 @@
       <c r="B79" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -24068,12 +24287,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -25311,12 +25530,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -26218,12 +26437,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -30100,12 +30319,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -30352,12 +30571,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -35239,12 +35458,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -42184,12 +42403,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec. || TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>A-tým Baník Třinec. Smart fix prev: chybělo → 52/53 0475 (Sokol Železárny VMM Třinec). Identity transition Sokol Železárny VMM → Baník (D28) + zkrácení názvu. || Baník Třinec 53/54 (30_Ostravský). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Třinec = HC Oceláři Třinec (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Třinec (1929) -&gt; KS Zaolzie (1938-39, Klub Sportowy Zaolzie - polske obdobi po Mnichove, Zaolzie = ceske uzemi za Olzou) -&gt; SK Železárny Třinec (1939) -&gt; TJ TŽ VŘSR Třinec (1950, VŘSR = Velke rijnove socialisticke revoluce, TŽ = Třinecké železárny) -&gt; TJ TŽ Třinec (1988, vypustil VŘSR) -&gt; HC Železárny Třinec (1994) -&gt; HC Oceláři Třinec (1999-dnes). POZN: Almanach 50/51 'Železárny Molotova Třinec' = TJ TŽ Molotov / VMM = patron Vjaceslav Molotov (nikoli VŘSR jak Wiki) - pravdepodobne kolega zaznamenal jinou variantu nazvu. Patterns: Železárny Molotova Třinec, Sokol Železárny VMM Třinec, Baník Třinec, TŽ Třinec. city Třinec. || Třinec = HC Oceláři Třinec (Wiki D42 - registr ustavy 04/2026). Vsechny trinecke kluby. Hlavni chain: TŽ (Třinecké železárny) Třinec -&gt; Banik Třinec -&gt; Sokol -&gt; Spartak -&gt; Banik -&gt; ZSJ TŽ -&gt; HC Oceláři Třinec. OUPZ Třinec III = paralelni. city Třinec.</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Český Těšín</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -43195,12 +43414,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -44937,7 +45156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -45011,12 +45230,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0010</t>
+          <t>CLUB_S1997_98_0019</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45031,12 +45250,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0019</t>
+          <t>CLUB_S1997_98_0026</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45051,12 +45270,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0026</t>
+          <t>CLUB_S1997_98_0051</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45071,12 +45290,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0041</t>
+          <t>CLUB_S1997_98_0053</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0467 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45091,12 +45310,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0051</t>
+          <t>CLUB_S1997_98_0055</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -45111,12 +45330,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0053</t>
+          <t>CLUB_S1997_98_0063</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0467 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45131,12 +45350,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0055</t>
+          <t>CLUB_S1997_98_0068</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45151,12 +45370,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0062</t>
+          <t>CLUB_S1997_98_0155</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45171,12 +45390,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0063</t>
+          <t>CLUB_S1997_98_0166</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45191,12 +45410,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0068</t>
+          <t>CLUB_S1997_98_0167</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45211,12 +45430,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0149</t>
+          <t>CLUB_S1997_98_0174</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45231,12 +45450,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0155</t>
+          <t>CLUB_S1997_98_0175</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45251,12 +45470,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0155</t>
+          <t>CLUB_S1997_98_0177</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45271,12 +45490,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0166</t>
+          <t>CLUB_S1997_98_0188</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45291,12 +45510,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0167</t>
+          <t>CLUB_S1997_98_0205</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45311,12 +45530,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0174</t>
+          <t>CLUB_S1997_98_0234</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45331,12 +45550,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0175</t>
+          <t>CLUB_S1997_98_0242</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45351,12 +45570,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0177</t>
+          <t>CLUB_S1997_98_0243</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tachov + Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45371,12 +45590,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0188</t>
+          <t>CLUB_S1997_98_0245</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45391,12 +45610,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0205</t>
+          <t>CLUB_S1997_98_0254</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0266 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45411,12 +45630,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0234</t>
+          <t>CLUB_S1997_98_0256</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45431,12 +45650,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0242</t>
+          <t>CLUB_S1997_98_0258</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -45451,12 +45670,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0243</t>
+          <t>CLUB_S1997_98_0270</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tachov + Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0275 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45471,12 +45690,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0245</t>
+          <t>CLUB_S1997_98_0278</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -45491,12 +45710,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0254</t>
+          <t>CLUB_S1997_98_0296</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0266 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -45511,12 +45730,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0256</t>
+          <t>CLUB_S1997_98_0308</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -45531,12 +45750,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0258</t>
+          <t>CLUB_S1997_98_0402</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45551,12 +45770,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0269</t>
+          <t>CLUB_S1997_98_0403</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45571,12 +45790,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0270</t>
+          <t>CLUB_S1997_98_0413</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0275 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0423 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45591,12 +45810,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0278</t>
+          <t>CLUB_S1997_98_0453</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0446 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45611,12 +45830,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0296</t>
+          <t>CLUB_S1997_98_0459</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45631,12 +45850,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0308</t>
+          <t>CLUB_S1997_98_0480</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>TBD: city 'Škoda Team Šumperk' → 'Šumperk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -45651,12 +45870,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0402</t>
+          <t>CLUB_S1997_98_0483</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0261 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45671,12 +45890,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0403</t>
+          <t>CLUB_S1997_98_0484</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0471 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -45691,177 +45910,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1997_98_0413</t>
+          <t>CLUB_S1997_98_0485</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0423 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1997_98_0427</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Třinec' → 'Český Těšín' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1997_98_0450</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1997_98_0453</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0446 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1997_98_0459</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1997_98_0480</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Škoda Team Šumperk' → 'Šumperk' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1997_98_0483</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0261 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1997_98_0484</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0471 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1997_98_0485</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0213 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F45"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -49252,7 +49252,7 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M29" t="n">
         <v>27</v>
@@ -49967,7 +49967,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M34" t="n">
         <v>21</v>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -18543,7 +18543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18607,6 +18607,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21801,8 +21811,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -21932,7 +21940,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -18795,6 +18795,16 @@
           <t>NODE_S1997_98_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18809,6 +18819,14 @@
         <is>
           <t>NODE_S1996_97_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -18983,6 +19001,16 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18997,6 +19025,14 @@
         <is>
           <t>NODE_S1996_97_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -19077,6 +19113,16 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19091,6 +19137,14 @@
         <is>
           <t>NODE_S1996_97_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -19124,6 +19178,16 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19138,6 +19202,14 @@
         <is>
           <t>NODE_S1996_97_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -19171,6 +19243,8 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19185,6 +19259,14 @@
         <is>
           <t>NODE_S1996_97_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -19218,6 +19300,8 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19232,6 +19316,14 @@
         <is>
           <t>NODE_S1996_97_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -19265,6 +19357,8 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19279,6 +19373,14 @@
         <is>
           <t>NODE_S1996_97_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -19312,6 +19414,8 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19326,6 +19430,14 @@
         <is>
           <t>NODE_S1996_97_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -19359,6 +19471,8 @@
           <t>NODE_S1997_98_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19373,6 +19487,14 @@
         <is>
           <t>NODE_S1996_97_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -19406,6 +19528,8 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19420,6 +19544,14 @@
         <is>
           <t>NODE_S1996_97_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -19453,6 +19585,8 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19467,6 +19601,14 @@
         <is>
           <t>NODE_S1996_97_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -19500,6 +19642,16 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19514,6 +19666,14 @@
         <is>
           <t>NODE_S1996_97_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -19641,6 +19801,12 @@
           <t>NODE_S1997_98_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19655,6 +19821,14 @@
         <is>
           <t>NODE_S1996_97_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -19688,6 +19862,12 @@
           <t>NODE_S1997_98_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19702,6 +19882,14 @@
         <is>
           <t>NODE_S1996_97_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -19735,6 +19923,12 @@
           <t>NODE_S1997_98_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19749,6 +19943,14 @@
         <is>
           <t>NODE_S1996_97_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -19782,6 +19984,12 @@
           <t>NODE_S1997_98_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19796,6 +20004,14 @@
         <is>
           <t>NODE_S1996_97_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -19829,6 +20045,8 @@
           <t>NODE_S1997_98_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19843,6 +20061,14 @@
         <is>
           <t>NODE_S1996_97_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -20482,6 +20708,12 @@
           <t>NODE_S1997_98_0040</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0044</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20496,6 +20728,14 @@
         <is>
           <t>NODE_S1996_97_0042</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -20571,6 +20811,8 @@
           <t>NODE_S1997_98_0040</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20585,6 +20827,14 @@
         <is>
           <t>NODE_S1996_97_0044</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -21412,6 +21662,16 @@
           <t>NODE_S1997_98_0060</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0068</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0064</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21421,6 +21681,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -21496,6 +21764,8 @@
           <t>NODE_S1997_98_0060</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21505,6 +21775,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>7.–11. ZČ</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -21664,6 +21942,8 @@
           <t>NODE_S1997_98_0060</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21673,6 +21953,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -21811,6 +22099,8 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -21940,6 +22230,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -753,6 +753,11 @@
           <t>HC Petra Vsetín (C)</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
@@ -19243,8 +19248,6 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19300,8 +19303,6 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19357,8 +19358,6 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19414,8 +19413,6 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19471,8 +19468,6 @@
           <t>NODE_S1997_98_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19528,8 +19523,6 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19585,8 +19578,6 @@
           <t>NODE_S1997_98_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19806,7 +19797,6 @@
           <t>NODE_S1997_98_0023</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19867,7 +19857,6 @@
           <t>NODE_S1997_98_0024</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19928,7 +19917,6 @@
           <t>NODE_S1997_98_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19989,7 +19977,6 @@
           <t>NODE_S1997_98_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20045,8 +20032,6 @@
           <t>NODE_S1997_98_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20708,7 +20693,6 @@
           <t>NODE_S1997_98_0040</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>NODE_S1997_98_0044</t>
@@ -20811,8 +20795,6 @@
           <t>NODE_S1997_98_0040</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21764,8 +21746,6 @@
           <t>NODE_S1997_98_0060</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21942,8 +21922,6 @@
           <t>NODE_S1997_98_0060</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22099,8 +22077,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -22230,7 +22206,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -45200,7 +45175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45440,6 +45415,18 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>1. utkání baráže Přerov - Kadaň bylo nedohráno a kontumováno 0:5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HC Petra Vsetín</t>
         </is>
       </c>
     </row>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -22077,6 +22077,8 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -22206,6 +22208,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -28728,8 +28739,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -28859,7 +28868,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -60502,7 +60510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -60559,7 +60567,7 @@
           <t>CLUB_S1997_98_0003</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60579,7 +60587,7 @@
           <t>CLUB_S1997_98_0019</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60599,7 +60607,7 @@
           <t>CLUB_S1997_98_0026</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60619,7 +60627,7 @@
           <t>CLUB_S1997_98_0051</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60639,7 +60647,7 @@
           <t>CLUB_S1997_98_0053</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0467 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -60659,7 +60667,7 @@
           <t>CLUB_S1997_98_0055</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -60679,7 +60687,7 @@
           <t>CLUB_S1997_98_0063</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60699,7 +60707,7 @@
           <t>CLUB_S1997_98_0068</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60719,7 +60727,7 @@
           <t>CLUB_S1997_98_0155</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60739,7 +60747,7 @@
           <t>CLUB_S1997_98_0166</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -60759,7 +60767,7 @@
           <t>CLUB_S1997_98_0167</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60779,7 +60787,7 @@
           <t>CLUB_S1997_98_0174</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60799,7 +60807,7 @@
           <t>CLUB_S1997_98_0175</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60819,7 +60827,7 @@
           <t>CLUB_S1997_98_0177</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60839,7 +60847,7 @@
           <t>CLUB_S1997_98_0188</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -60859,7 +60867,7 @@
           <t>CLUB_S1997_98_0205</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60879,7 +60887,7 @@
           <t>CLUB_S1997_98_0234</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -60899,7 +60907,7 @@
           <t>CLUB_S1997_98_0242</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0247 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -60919,7 +60927,7 @@
           <t>CLUB_S1997_98_0243</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Tachov + Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60939,7 +60947,7 @@
           <t>CLUB_S1997_98_0245</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -60959,7 +60967,7 @@
           <t>CLUB_S1997_98_0254</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0266 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -60979,7 +60987,7 @@
           <t>CLUB_S1997_98_0256</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -60999,7 +61007,7 @@
           <t>CLUB_S1997_98_0258</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -61019,7 +61027,7 @@
           <t>CLUB_S1997_98_0270</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0275 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61039,7 +61047,7 @@
           <t>CLUB_S1997_98_0278</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -61059,7 +61067,7 @@
           <t>CLUB_S1997_98_0296</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -61079,7 +61087,7 @@
           <t>CLUB_S1997_98_0308</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -61099,7 +61107,7 @@
           <t>CLUB_S1997_98_0402</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61119,7 +61127,7 @@
           <t>CLUB_S1997_98_0403</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61139,7 +61147,7 @@
           <t>CLUB_S1997_98_0413</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0423 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61159,7 +61167,7 @@
           <t>CLUB_S1997_98_0453</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0446 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61179,7 +61187,7 @@
           <t>CLUB_S1997_98_0459</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61199,7 +61207,7 @@
           <t>CLUB_S1997_98_0480</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: city 'Škoda Team Šumperk' → 'Šumperk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61219,7 +61227,7 @@
           <t>CLUB_S1997_98_0483</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0261 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61239,7 +61247,7 @@
           <t>CLUB_S1997_98_0484</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0471 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -61259,11 +61267,37 @@
           <t>CLUB_S1997_98_0485</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1996_97_0213 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Středočeský – Regionální liga (Středočeský kraj) · NODE_S1997_98_0072</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Spartak Hořovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F37"/>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -24720,7 +24723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25194,6 +25197,23 @@
         </is>
       </c>
       <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NODE_S1997_98_0072</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Spartak Hořovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -61287,7 +61307,7 @@
           <t>Středočeský – Regionální liga (Středočeský kraj) · NODE_S1997_98_0072</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Spartak Hořovice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -26850,7 +26850,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -26897,7 +26897,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -27216,7 +27216,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -27263,7 +27263,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -27310,7 +27310,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Regionální liga</t>
+          <t>Středočeský, 4. úroveň Regionální liga</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -27352,7 +27352,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finálová skupina</t>
+          <t>Středočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 o udržení</t>
+          <t>Středočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -27509,7 +27509,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -27603,7 +27603,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Krajská soutěž</t>
+          <t>Jihočeský, 4. úroveň Krajská soutěž</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -27650,7 +27650,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -27744,7 +27744,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 Krajská soutěž</t>
+          <t>Západočeský, 4. úroveň Krajská soutěž</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina A</t>
+          <t>Západočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -27838,7 +27838,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina B</t>
+          <t>Západočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina C</t>
+          <t>Západočeský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -27927,7 +27927,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -28021,7 +28021,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -28115,7 +28115,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 skupina Sever</t>
+          <t>Východočeský, 5. úroveň, skupina Sever</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -28162,7 +28162,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 skupina Jih</t>
+          <t>Východočeský, 5. úroveň, skupina Jih</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -28363,7 +28363,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -28405,7 +28405,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení</t>
+          <t>Jihomoravský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Krajská soutěž</t>
+          <t>Jihomoravský, 4. úroveň Krajská soutěž</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -28539,7 +28539,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -28581,7 +28581,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -28631,7 +28631,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -28725,7 +28725,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 Krajská soutěž</t>
+          <t>Severomoravský, 4. úroveň Krajská soutěž</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -28759,6 +28759,8 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -28791,7 +28793,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -28888,6 +28890,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>

--- a/data/S1997_98_FINAL.xlsx
+++ b/data/S1997_98_FINAL.xlsx
@@ -10364,7 +10364,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -28759,8 +28759,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -28890,7 +28888,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
